--- a/ttl_long/AdHoc_Net_1.xlsx
+++ b/ttl_long/AdHoc_Net_1.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>391</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>255</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>266</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>342</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>367</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>395</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>383</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>497</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>163</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>549</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>540</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>553</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>573</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>643</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>788</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>753</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>710</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>769</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>807</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>921</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>902</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>940</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1112</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1041</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1026</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1177</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1181</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1133</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1263</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1313</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1217</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1385</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1359</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,131 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>391</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1359</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1559</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1694</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,7 +1334,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1237,7 +1356,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1259,7 +1378,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1281,7 +1400,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1303,7 +1422,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1325,7 +1444,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1347,7 +1466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1369,7 +1488,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1391,7 +1510,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1408,12 +1527,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1435,7 +1554,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1457,7 +1576,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1474,12 +1593,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,7 +1620,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1523,7 +1642,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1545,7 +1664,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1567,7 +1686,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1708,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1606,12 +1725,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1633,7 +1752,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1655,7 +1774,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1672,12 +1791,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1694,12 +1813,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1721,7 +1840,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1738,12 +1857,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1760,12 +1879,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1782,12 +1901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1809,7 +1928,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1826,12 +1945,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1848,12 +1967,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1870,12 +1989,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1892,12 +2011,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1914,12 +2033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1936,12 +2055,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1958,12 +2077,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1980,12 +2099,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2002,12 +2121,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2024,12 +2143,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2046,12 +2165,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2068,12 +2187,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2090,12 +2209,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2112,12 +2231,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2134,12 +2253,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2156,12 +2275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2178,12 +2297,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2200,12 +2319,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2222,12 +2341,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2244,12 +2363,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2266,12 +2385,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2288,12 +2407,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2310,7 +2429,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2332,12 +2451,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2354,12 +2473,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2376,12 +2495,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2398,12 +2517,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2420,12 +2539,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,12 +2561,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2464,12 +2583,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2486,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2508,12 +2627,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2530,12 +2649,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2552,12 +2671,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2574,12 +2693,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2596,12 +2715,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2618,12 +2737,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2640,12 +2759,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2662,12 +2781,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2684,12 +2803,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2706,12 +2825,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2728,12 +2847,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2750,12 +2869,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2772,12 +2891,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2794,12 +2913,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2816,12 +2935,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2838,7 +2957,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2860,12 +2979,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2882,12 +3001,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2904,12 +3023,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2926,12 +3045,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2948,12 +3067,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2970,12 +3089,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2992,12 +3111,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3014,12 +3133,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3036,12 +3155,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3058,12 +3177,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3080,12 +3199,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3102,12 +3221,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3124,12 +3243,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3146,12 +3265,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3168,12 +3287,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3190,12 +3309,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3212,12 +3331,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3234,12 +3353,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3256,12 +3375,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3278,12 +3397,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3300,12 +3419,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3322,12 +3441,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3344,12 +3463,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3366,12 +3485,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3388,12 +3507,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3410,12 +3529,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3432,12 +3551,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3454,7 +3573,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3476,12 +3595,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3498,12 +3617,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3520,12 +3639,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3542,12 +3661,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3564,12 +3683,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3586,12 +3705,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3608,12 +3727,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3630,12 +3749,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3652,12 +3771,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3674,12 +3793,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3696,12 +3815,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3718,12 +3837,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3740,12 +3859,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3762,12 +3881,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3784,20 +3903,636 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3836,7 +4571,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3846,7 +4581,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -3872,7 +4607,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_1.xlsx
+++ b/ttl_long/AdHoc_Net_1.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>179</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>309</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>98</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>192</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>219</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>261</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>263</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>356</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>444</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>353</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>388</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>539</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>530</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>532</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>612</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>255</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>581</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>610</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>753</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>284</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>762</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>908</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>908</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>910</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1061</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>284</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>1083</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1206</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1102</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1216</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>263</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1272</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1223</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1414</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1446</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1362</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1449</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1481</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>224</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>558</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1690</t>
         </is>
       </c>
     </row>
@@ -1123,148 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>167</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1359</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1529</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1535</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1694</t>
+          <t>1533</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1422,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1444,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1461,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1488,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1576,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1593,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1620,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1642,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1659,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1681,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1725,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1752,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1774,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1791,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1840,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1857,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1884,7 +1748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1901,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1928,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1950,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1967,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1989,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2016,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2055,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2082,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2104,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2126,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2143,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2170,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2192,7 +2056,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2209,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2236,7 +2100,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2258,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2275,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2302,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2324,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2346,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2368,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2385,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2407,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2429,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2456,7 +2320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2473,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2495,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2517,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2544,7 +2408,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2561,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2583,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2610,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2632,7 +2496,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2654,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2671,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2693,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2715,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2737,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2759,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2786,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2825,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2852,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2874,7 +2738,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2896,7 +2760,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2913,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2940,7 +2804,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2962,7 +2826,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2979,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3023,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3045,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3067,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3111,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3133,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3155,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3177,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3199,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3221,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3243,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3265,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3287,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3309,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3331,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3353,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3375,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3419,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3441,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3463,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3485,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3507,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3529,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3556,7 +3420,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3595,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3622,7 +3486,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3644,7 +3508,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3666,7 +3530,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3683,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3710,7 +3574,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3732,7 +3596,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3754,7 +3618,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3771,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3793,12 +3657,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3815,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3842,7 +3706,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3864,7 +3728,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3886,7 +3750,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3908,7 +3772,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3925,12 +3789,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3947,12 +3811,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3969,12 +3833,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3991,12 +3855,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4005,534 +3869,6 @@
         </is>
       </c>
       <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4571,7 +3907,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -4581,7 +3917,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -4601,7 +3937,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_1.xlsx
+++ b/ttl_long/AdHoc_Net_1.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>186</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>322</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>272</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>331</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>325</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>345</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>456</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>263</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>487</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>339</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>511</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>648</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>675</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>599</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>747</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>733</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>775</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>873</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>840</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>860</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>960</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1076</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>974</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1038</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>259</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1032</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>316</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1128</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1323</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1236</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>293</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1268</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1289</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1377</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1471</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1441</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>1468</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1587</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1596</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,7 +2029,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,7 +2337,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,7 +3217,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3657,12 +3657,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3679,7 +3679,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3745,12 +3745,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3767,12 +3767,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3789,12 +3789,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3811,12 +3811,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3825,50 +3825,6 @@
         </is>
       </c>
       <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3907,7 +3863,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3917,7 +3873,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
